--- a/events/Poznan_2022_WC/Poznan_2022_WC_Results.xlsx
+++ b/events/Poznan_2022_WC/Poznan_2022_WC_Results.xlsx
@@ -1947,6 +1947,11 @@
           <t>64580</t>
         </is>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>61249</t>
+        </is>
+      </c>
       <c r="T21" t="inlineStr">
         <is>
           <t>118986</t>
@@ -13881,6 +13886,11 @@
           <t>00:01:55.000</t>
         </is>
       </c>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>61249</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -14975,6 +14985,11 @@
           <t>00:01:55.410</t>
         </is>
       </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>42444</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -17060,6 +17075,11 @@
           <t>64580</t>
         </is>
       </c>
+      <c r="S240" t="inlineStr">
+        <is>
+          <t>61249</t>
+        </is>
+      </c>
       <c r="T240" t="inlineStr">
         <is>
           <t>118986</t>
@@ -26296,6 +26316,11 @@
           <t>00:01:53.330</t>
         </is>
       </c>
+      <c r="R376" t="inlineStr">
+        <is>
+          <t>61249</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -26421,6 +26446,11 @@
           <t>00:01:54.190</t>
         </is>
       </c>
+      <c r="R378" t="inlineStr">
+        <is>
+          <t>42444</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -31403,6 +31433,11 @@
           <t>00:00:42.760</t>
         </is>
       </c>
+      <c r="R455" t="inlineStr">
+        <is>
+          <t>42444</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -40099,6 +40134,11 @@
           <t>00:01:47.150</t>
         </is>
       </c>
+      <c r="R584" t="inlineStr">
+        <is>
+          <t>61249</t>
+        </is>
+      </c>
       <c r="S584" t="inlineStr">
         <is>
           <t>118986</t>
@@ -47377,6 +47417,11 @@
           <t>00:00:40.980</t>
         </is>
       </c>
+      <c r="R698" t="inlineStr">
+        <is>
+          <t>42444</t>
+        </is>
+      </c>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
@@ -54370,6 +54415,11 @@
           <t>00:01:44.300</t>
         </is>
       </c>
+      <c r="R803" t="inlineStr">
+        <is>
+          <t>61249</t>
+        </is>
+      </c>
       <c r="S803" t="inlineStr">
         <is>
           <t>118986</t>
@@ -57032,6 +57082,11 @@
           <t>00:01:35.930</t>
         </is>
       </c>
+      <c r="R842" t="inlineStr">
+        <is>
+          <t>61249</t>
+        </is>
+      </c>
       <c r="S842" t="inlineStr">
         <is>
           <t>94097</t>
@@ -61278,6 +61333,11 @@
           <t>64580</t>
         </is>
       </c>
+      <c r="S905" t="inlineStr">
+        <is>
+          <t>61249</t>
+        </is>
+      </c>
       <c r="T905" t="inlineStr">
         <is>
           <t>118986</t>
@@ -66504,6 +66564,11 @@
           <t>00:01:50.760</t>
         </is>
       </c>
+      <c r="R977" t="inlineStr">
+        <is>
+          <t>61249</t>
+        </is>
+      </c>
     </row>
     <row r="978">
       <c r="A978" t="inlineStr">
@@ -66700,6 +66765,11 @@
           <t>00:01:52.460</t>
         </is>
       </c>
+      <c r="R980" t="inlineStr">
+        <is>
+          <t>42444</t>
+        </is>
+      </c>
     </row>
     <row r="981">
       <c r="A981" t="inlineStr">
@@ -73015,6 +73085,11 @@
           <t>00:00:41.030</t>
         </is>
       </c>
+      <c r="R1075" t="inlineStr">
+        <is>
+          <t>42444</t>
+        </is>
+      </c>
     </row>
     <row r="1076">
       <c r="A1076" t="inlineStr">
@@ -75722,6 +75797,11 @@
           <t>00:01:43.800</t>
         </is>
       </c>
+      <c r="R1114" t="inlineStr">
+        <is>
+          <t>61249</t>
+        </is>
+      </c>
       <c r="S1114" t="inlineStr">
         <is>
           <t>118986</t>
@@ -78097,6 +78177,11 @@
           <t>00:01:36.830</t>
         </is>
       </c>
+      <c r="R1148" t="inlineStr">
+        <is>
+          <t>61249</t>
+        </is>
+      </c>
       <c r="S1148" t="inlineStr">
         <is>
           <t>94097</t>
@@ -81928,6 +82013,11 @@
       </c>
       <c r="L1207" t="n">
         <v>17</v>
+      </c>
+      <c r="R1207" t="inlineStr">
+        <is>
+          <t>61249</t>
+        </is>
       </c>
       <c r="X1207" t="inlineStr">
         <is>
@@ -84243,7 +84333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D523"/>
+  <dimension ref="A1:D525"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -95752,6 +95842,50 @@
         </is>
       </c>
     </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>61249</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>Alyssa</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>BULL</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>42444</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>Anja</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>OSTERMAN</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Poznan_2022_WC/Poznan_2022_WC_Results.xlsx
+++ b/events/Poznan_2022_WC/Poznan_2022_WC_Results.xlsx
@@ -12321,6 +12321,11 @@
           <t>00:02:12.500</t>
         </is>
       </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>72815</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -43674,6 +43679,11 @@
           <t>00:01:18.250</t>
         </is>
       </c>
+      <c r="R638" t="inlineStr">
+        <is>
+          <t>122323</t>
+        </is>
+      </c>
     </row>
     <row r="639">
       <c r="B639" t="inlineStr">
@@ -43782,6 +43792,16 @@
           <t>00:01:20.660</t>
         </is>
       </c>
+      <c r="R640" t="inlineStr">
+        <is>
+          <t>161203</t>
+        </is>
+      </c>
+      <c r="S640" t="inlineStr">
+        <is>
+          <t>144523</t>
+        </is>
+      </c>
     </row>
     <row r="641">
       <c r="B641" t="inlineStr">
@@ -43890,6 +43910,16 @@
           <t>00:01:27.010</t>
         </is>
       </c>
+      <c r="R642" t="inlineStr">
+        <is>
+          <t>42511</t>
+        </is>
+      </c>
+      <c r="S642" t="inlineStr">
+        <is>
+          <t>144812</t>
+        </is>
+      </c>
     </row>
     <row r="643">
       <c r="B643" t="inlineStr">
@@ -44052,6 +44082,11 @@
           <t>00:01:42.510</t>
         </is>
       </c>
+      <c r="S645" t="inlineStr">
+        <is>
+          <t>134225</t>
+        </is>
+      </c>
     </row>
     <row r="646">
       <c r="B646" t="inlineStr">
@@ -44106,6 +44141,11 @@
           <t>00:01:10.810</t>
         </is>
       </c>
+      <c r="S646" t="inlineStr">
+        <is>
+          <t>134225</t>
+        </is>
+      </c>
     </row>
     <row r="647">
       <c r="B647" t="inlineStr">
@@ -44160,6 +44200,16 @@
           <t>00:01:12.630</t>
         </is>
       </c>
+      <c r="R647" t="inlineStr">
+        <is>
+          <t>122322</t>
+        </is>
+      </c>
+      <c r="S647" t="inlineStr">
+        <is>
+          <t>144812</t>
+        </is>
+      </c>
     </row>
     <row r="648">
       <c r="B648" t="inlineStr">
@@ -44376,6 +44426,11 @@
           <t>00:01:34.210</t>
         </is>
       </c>
+      <c r="R651" t="inlineStr">
+        <is>
+          <t>172159</t>
+        </is>
+      </c>
     </row>
     <row r="652">
       <c r="B652" t="inlineStr">
@@ -44430,6 +44485,11 @@
           <t>00:01:38.920</t>
         </is>
       </c>
+      <c r="R652" t="inlineStr">
+        <is>
+          <t>134661</t>
+        </is>
+      </c>
     </row>
     <row r="653">
       <c r="B653" t="inlineStr">
@@ -57539,6 +57599,11 @@
           <t>00:01:13.810</t>
         </is>
       </c>
+      <c r="R849" t="inlineStr">
+        <is>
+          <t>71957</t>
+        </is>
+      </c>
     </row>
     <row r="850">
       <c r="B850" t="inlineStr">
@@ -57596,6 +57661,11 @@
           <t>00:01:14.160</t>
         </is>
       </c>
+      <c r="R850" t="inlineStr">
+        <is>
+          <t>105917</t>
+        </is>
+      </c>
     </row>
     <row r="851">
       <c r="B851" t="inlineStr">
@@ -57653,6 +57723,11 @@
           <t>00:01:15.700</t>
         </is>
       </c>
+      <c r="R851" t="inlineStr">
+        <is>
+          <t>35871</t>
+        </is>
+      </c>
     </row>
     <row r="852">
       <c r="B852" t="inlineStr">
@@ -57767,6 +57842,11 @@
           <t>00:01:26.490</t>
         </is>
       </c>
+      <c r="R853" t="inlineStr">
+        <is>
+          <t>114708</t>
+        </is>
+      </c>
     </row>
     <row r="854">
       <c r="B854" t="inlineStr">
@@ -57881,6 +57961,11 @@
           <t>00:01:44.760</t>
         </is>
       </c>
+      <c r="R855" t="inlineStr">
+        <is>
+          <t>42599</t>
+        </is>
+      </c>
     </row>
     <row r="856">
       <c r="A856" t="inlineStr">
@@ -65668,6 +65753,11 @@
           <t>00:02:08.220</t>
         </is>
       </c>
+      <c r="R964" t="inlineStr">
+        <is>
+          <t>72815</t>
+        </is>
+      </c>
     </row>
     <row r="965">
       <c r="A965" t="inlineStr">
@@ -77519,6 +77609,11 @@
       <c r="R1139" t="inlineStr">
         <is>
           <t>46394</t>
+        </is>
+      </c>
+      <c r="S1139" t="inlineStr">
+        <is>
+          <t>72815</t>
         </is>
       </c>
     </row>
@@ -84303,7 +84398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D525"/>
+  <dimension ref="A1:D540"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -95856,6 +95951,336 @@
         </is>
       </c>
     </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>35871</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>Piotr</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>KULETA</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>42511</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>Martin</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>SCHUBERT</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>42599</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>Grzegorz</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>SZPYNDA</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>71957</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>Patryk</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>KOWALSKI</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>72815</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>Anastasiia</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>RYBACHOK</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>105917</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>Jakub</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>SITKOWSKI</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>114708</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>KLIMASZYK</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>122322</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>Leona</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>JOHS</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>122323</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>Sebastian</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>GIRKE</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>134225</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>Thomas</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>BROCKMANN</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>134661</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>Jacek</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>MAZANOWSKI</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>144523</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>Stefan</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>GLAWE</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>144812</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>Rado</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>JOHS</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>161203</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>Johannes</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>SCHWENZER</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>172159</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>Justin</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>VANDREE</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
